--- a/locations_Thành_phố_Phú_Quốc_20260319_2143.xlsx
+++ b/locations_Thành_phố_Phú_Quốc_20260319_2143.xlsx
@@ -1,41 +1,461 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\MyTool\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A245C328-4D00-4BFA-BC8C-CCB68F1EFE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Locations" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="143">
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Địa chỉ cụ thể</t>
+  </si>
+  <si>
+    <t>Tỉnh/Thành phố</t>
+  </si>
+  <si>
+    <t>Phường/Xã</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>9 Đường MILAN</t>
+  </si>
+  <si>
+    <t>Tỉnh Kiên Giang</t>
+  </si>
+  <si>
+    <t>Sunset Town</t>
+  </si>
+  <si>
+    <t>40 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Tỉnh An Giang</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>90 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>129 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>89 Tran Hung Dao</t>
+  </si>
+  <si>
+    <t>98 Tran Hung Dao</t>
+  </si>
+  <si>
+    <t>127 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>101/5 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>AT98 New An Thới</t>
+  </si>
+  <si>
+    <t>An Thới</t>
+  </si>
+  <si>
+    <t>103 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Tỉnh Kien Giang</t>
+  </si>
+  <si>
+    <t>Duong Dong</t>
+  </si>
+  <si>
+    <t>151A Đường 30/4</t>
+  </si>
+  <si>
+    <t>26 Lý Thường Kiệt</t>
+  </si>
+  <si>
+    <t>118 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>To 3 Lê Thuc Nha</t>
+  </si>
+  <si>
+    <t>Cua Duong</t>
+  </si>
+  <si>
+    <t>100C/4 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Dương Đông</t>
+  </si>
+  <si>
+    <t>17 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>30 Thang 4</t>
+  </si>
+  <si>
+    <t>99A 99A Đường Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>447 Nguyễn Văn Cừ</t>
+  </si>
+  <si>
+    <t>163 Lý Thường Kệt</t>
+  </si>
+  <si>
+    <t>01 Cầu Bà Phong Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Ven 02 Venice</t>
+  </si>
+  <si>
+    <t>119 Ba Mươi Tháng Tư</t>
+  </si>
+  <si>
+    <t>144A 30 tháng 4</t>
+  </si>
+  <si>
+    <t>Tỉnh Phú Quốc</t>
+  </si>
+  <si>
+    <t>thị trấn Dương Đông</t>
+  </si>
+  <si>
+    <t>76/4 30/04 street;Đường 30/4</t>
+  </si>
+  <si>
+    <t>92a Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>143 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>97 Tran Hung Dao Street</t>
+  </si>
+  <si>
+    <t>Tỉnh Phu Quoc Island</t>
+  </si>
+  <si>
+    <t>149 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>105 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>127D Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>73 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>47 Ham Ninh Fishervillage, Highway 47</t>
+  </si>
+  <si>
+    <t>5 Tố</t>
+  </si>
+  <si>
+    <t>Tỉnh Kiến Giang, Vietnam</t>
+  </si>
+  <si>
+    <t>ấp Suổc Mây</t>
+  </si>
+  <si>
+    <t>126 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>91/10 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Tỉnh Phu Quoc</t>
+  </si>
+  <si>
+    <t>SK Hotel,MP-135 Marina Square, BIM Group, Ấp Đường Bào, Dương Tơ, Phú Quốc, Kiên Gia</t>
+  </si>
+  <si>
+    <t>98/1 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>180 Nguyễn Trung Trực</t>
+  </si>
+  <si>
+    <t>6 Lý Tự Trọng</t>
+  </si>
+  <si>
+    <t>91/? Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>63 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>81 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>139 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>96 Nguyễn Trung Trực</t>
+  </si>
+  <si>
+    <t>Alley 118 Alley 118, Tran Hung Dao Street</t>
+  </si>
+  <si>
+    <t>141A Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Khu Phố 7</t>
+  </si>
+  <si>
+    <t>155 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>DƯƠNG ĐÔNG</t>
+  </si>
+  <si>
+    <t>242 Nguyễn Trung Trực</t>
+  </si>
+  <si>
+    <t>114 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>69 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>157 Nguyễn Văn Cừ</t>
+  </si>
+  <si>
+    <t>136 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Tỉnh KIÊN GIANG</t>
+  </si>
+  <si>
+    <t>DƯƠNG TƠ</t>
+  </si>
+  <si>
+    <t>DĐ 37 Night Market</t>
+  </si>
+  <si>
+    <t>102 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>111/9 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>6 Mạc Cửu</t>
+  </si>
+  <si>
+    <t>225 Trần Phú</t>
+  </si>
+  <si>
+    <t>5XQF+XHJ Kam pốt</t>
+  </si>
+  <si>
+    <t>32A Bạch Đằng</t>
+  </si>
+  <si>
+    <t>88/1 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>99 Tran Hung Dao</t>
+  </si>
+  <si>
+    <t>Số AT 96 Đại Lộ New An Thới</t>
+  </si>
+  <si>
+    <t>118/3 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Ấp 5 Đường Bào</t>
+  </si>
+  <si>
+    <t>84 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>ĐTH1-18 Địa Trung Hải 1</t>
+  </si>
+  <si>
+    <t>Thành phố Phú Quốc</t>
+  </si>
+  <si>
+    <t>Grand World Phú Quốc</t>
+  </si>
+  <si>
+    <t>54 Le Thuc Nha</t>
+  </si>
+  <si>
+    <t>Ong Lang</t>
+  </si>
+  <si>
+    <t>60-62 Nguyễn Văn Cừ</t>
+  </si>
+  <si>
+    <t>Tỉnh An Thoi</t>
+  </si>
+  <si>
+    <t>100/3 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Khu phố 7</t>
+  </si>
+  <si>
+    <t>91/1 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>2/1/118 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>116 116 tran hung dao</t>
+  </si>
+  <si>
+    <t>108 Đường 30/4</t>
+  </si>
+  <si>
+    <t>77 khu phố 1 Nguyễn Trường Tộ</t>
+  </si>
+  <si>
+    <t>3 Bãi</t>
+  </si>
+  <si>
+    <t>Ông Lang</t>
+  </si>
+  <si>
+    <t>Tổ 7, Ấp Suối Đá Tuyến tránh Dương Đông</t>
+  </si>
+  <si>
+    <t>Xã Dương Tơ</t>
+  </si>
+  <si>
+    <t>100 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>106 Tran Hung Dao</t>
+  </si>
+  <si>
+    <t>62 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>19 Venice Street</t>
+  </si>
+  <si>
+    <t>127/2 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>47/9 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>1 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>tổ 7 đường Dinh Bà</t>
+  </si>
+  <si>
+    <t>81 b Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>99A Tran Hung Dao</t>
+  </si>
+  <si>
+    <t>118/2 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>SS13-S01 Khu phố đi bộ Sona sea, Phú Quốc</t>
+  </si>
+  <si>
+    <t>H1-H2 Cầu Hôn</t>
+  </si>
+  <si>
+    <t>5 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>143 Tran Hung Dao Street</t>
+  </si>
+  <si>
+    <t>43 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>91/4 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>118/18 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>141 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>1 Đường Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Khu Phố Dương Tơ</t>
+  </si>
+  <si>
+    <t>Tổ 3 Lê Thúc Nha</t>
+  </si>
+  <si>
+    <t>ấp Ông Lang</t>
+  </si>
+  <si>
+    <t>3 Đường tỉnh 975</t>
+  </si>
+  <si>
+    <t>6 Bạch Đằng</t>
+  </si>
+  <si>
+    <t>Tỉnh Dương Đông</t>
+  </si>
+  <si>
+    <t>121 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Kiên Giang</t>
+  </si>
+  <si>
+    <t>Lot 4 Ong Lang Hamlet</t>
+  </si>
+  <si>
+    <t>100C/4A Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>Hamlet 4 Cua Can Commune</t>
+  </si>
+  <si>
+    <t>Tỉnh Vietnam</t>
+  </si>
+  <si>
+    <t>233 Nguyễn Trung Trực</t>
+  </si>
+  <si>
+    <t>khu phố 5</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +485,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,49 +824,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F117"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="36.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.875" customWidth="1"/>
+    <col min="2" max="2" width="36.875" customWidth="1"/>
+    <col min="3" max="3" width="24.875" customWidth="1"/>
+    <col min="4" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="6" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>STT</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Địa chỉ cụ thể</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Tỉnh/Thành phố</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Phường/Xã</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Latitude</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Longitude</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>9 Đường MILAN</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Sunset Town</v>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
       </c>
       <c r="E2">
         <v>10.0257144</v>
@@ -447,38 +875,38 @@
         <v>104.0088734</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>40 Trần Hưng Đạo</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>10.2133815</v>
+        <v>10.213381500000001</v>
       </c>
       <c r="F3">
         <v>103.958825</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>90 Trần Hưng Đạo</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
       </c>
       <c r="E4">
         <v>10.2046358</v>
@@ -487,38 +915,38 @@
         <v>103.9638125</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>129 Trần Hưng Đạo</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
       </c>
       <c r="E5">
         <v>10.1975161</v>
       </c>
       <c r="F5">
-        <v>103.9686357</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>103.96863569999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>89 Tran Hung Dao</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
       </c>
       <c r="E6">
         <v>10.2054648</v>
@@ -527,78 +955,78 @@
         <v>103.9640814</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>98 Tran Hung Dao</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
       </c>
       <c r="E7">
         <v>10.2017822</v>
       </c>
       <c r="F7">
-        <v>103.9633392</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>103.96333919999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>127 Trần Hưng Đạo</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
       </c>
       <c r="E8">
         <v>10.1965203</v>
       </c>
       <c r="F8">
-        <v>103.9716613</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>103.97166129999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>101/5 Trần Hưng Đạo</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
       </c>
       <c r="E9">
         <v>10.2055989</v>
       </c>
       <c r="F9">
-        <v>103.9666595</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>103.96665950000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>AT98 New An Thới</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D10" t="str">
-        <v>An Thới</v>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
       </c>
       <c r="E10">
         <v>10.0361759</v>
@@ -607,78 +1035,78 @@
         <v>104.0068538</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>103 Trần Hưng Đạo</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Tỉnh Kien Giang</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Duong Dong</v>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
       </c>
       <c r="E11">
-        <v>10.2034832</v>
+        <v>10.203483200000001</v>
       </c>
       <c r="F11">
         <v>103.9646836</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>151A Đường 30/4</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
       </c>
       <c r="E12">
-        <v>10.2137819</v>
+        <v>10.213781900000001</v>
       </c>
       <c r="F12">
         <v>103.9648997</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>26 Lý Thường Kiệt</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
       </c>
       <c r="E13">
-        <v>10.2242542</v>
+        <v>10.224254200000001</v>
       </c>
       <c r="F13">
         <v>103.9666711</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>118 Trần Hưng Đạo</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D14" t="str">
-        <v/>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
       </c>
       <c r="E14">
         <v>10.1949638</v>
@@ -687,58 +1115,58 @@
         <v>103.9673172</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>To 3 Lê Thuc Nha</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Tỉnh Kien Giang</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Cua Duong</v>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
       </c>
       <c r="E15">
-        <v>10.2593676</v>
+        <v>10.259367599999999</v>
       </c>
       <c r="F15">
         <v>103.9380634</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>100C/4 Trần Hưng Đạo</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Dương Đông</v>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
       </c>
       <c r="E16">
         <v>10.2001735</v>
       </c>
       <c r="F16">
-        <v>103.9644934</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>103.96449339999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>17 Trần Hưng Đạo</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D17" t="str">
-        <v/>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
       </c>
       <c r="E17">
         <v>10.2141132</v>
@@ -747,18 +1175,18 @@
         <v>103.9593163</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>30 Thang 4</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D18" t="str">
-        <v/>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
       </c>
       <c r="E18">
         <v>10.2138446</v>
@@ -767,18 +1195,18 @@
         <v>103.9663857</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>99A 99A Đường Trần Hưng Đạo</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D19" t="str">
-        <v/>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
       </c>
       <c r="E19">
         <v>10.2039188</v>
@@ -787,78 +1215,78 @@
         <v>103.9645403</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>447 Nguyễn Văn Cừ</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D20" t="str">
-        <v/>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
       </c>
       <c r="E20">
         <v>10.0398704</v>
       </c>
       <c r="F20">
-        <v>104.0172753</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>104.01727529999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>163 Lý Thường Kệt</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D21" t="str">
-        <v/>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
       </c>
       <c r="E21">
-        <v>10.2258565</v>
+        <v>10.225856500000001</v>
       </c>
       <c r="F21">
         <v>103.9749522</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="str">
-        <v>01 Cầu Bà Phong Trần Hưng Đạo</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D22" t="str">
-        <v/>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
       </c>
       <c r="E22">
         <v>10.1850158</v>
       </c>
       <c r="F22">
-        <v>103.9681345</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>103.96813450000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="str">
-        <v>Ven 02 Venice</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Sunset Town</v>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>8</v>
       </c>
       <c r="E23">
         <v>10.0300861</v>
@@ -867,58 +1295,58 @@
         <v>104.0061776</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="str">
-        <v>119 Ba Mươi Tháng Tư</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D24" t="str">
-        <v/>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
       </c>
       <c r="E24">
-        <v>10.2138988</v>
+        <v>10.213898800000001</v>
       </c>
       <c r="F24">
-        <v>103.9637497</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>103.96374969999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="str">
-        <v>144A 30 tháng 4</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Tỉnh Phú Quốc</v>
-      </c>
-      <c r="D25" t="str">
-        <v>thị trấn Dương Đông</v>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" t="s">
+        <v>40</v>
       </c>
       <c r="E25">
-        <v>10.2164741</v>
+        <v>10.216474099999999</v>
       </c>
       <c r="F25">
         <v>103.9692534</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="str">
-        <v>76/4 30/04 street;Đường 30/4</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D26" t="str">
-        <v/>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
       </c>
       <c r="E26">
         <v>10.211223</v>
@@ -927,18 +1355,18 @@
         <v>103.9651781</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="str">
-        <v>92a Trần Hưng Đạo</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D27" t="str">
-        <v/>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
       </c>
       <c r="E27">
         <v>10.2027997</v>
@@ -947,38 +1375,38 @@
         <v>103.9642917</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="str">
-        <v>143 Trần Hưng Đạo</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D28" t="str">
-        <v/>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
       </c>
       <c r="E28">
-        <v>10.1921779</v>
+        <v>10.192177900000001</v>
       </c>
       <c r="F28">
-        <v>103.9665575</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>103.96655749999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="str">
-        <v>97 Tran Hung Dao Street</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Tỉnh Phu Quoc Island</v>
-      </c>
-      <c r="D29" t="str">
-        <v/>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
       </c>
       <c r="E29">
         <v>10.208007</v>
@@ -987,78 +1415,78 @@
         <v>103.9625157</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v>149 Trần Hưng Đạo</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D30" t="str">
-        <v/>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
       </c>
       <c r="E30">
-        <v>10.1928796</v>
+        <v>10.192879599999999</v>
       </c>
       <c r="F30">
         <v>103.9673682</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="str">
-        <v>105 Trần Hưng Đạo</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D31" t="str">
-        <v/>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
       </c>
       <c r="E31">
-        <v>10.188408</v>
+        <v>10.188408000000001</v>
       </c>
       <c r="F31">
         <v>103.9691698</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="str">
-        <v>127D Trần Hưng Đạo</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D32" t="str">
-        <v/>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
       </c>
       <c r="E32">
-        <v>10.2001365</v>
+        <v>10.200136499999999</v>
       </c>
       <c r="F32">
-        <v>103.9735143</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>103.97351430000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="str">
-        <v>73 Trần Hưng Đạo</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D33" t="str">
-        <v/>
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
       </c>
       <c r="E33">
         <v>10.2061847</v>
@@ -1067,18 +1495,18 @@
         <v>103.963443</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="str">
-        <v>47 Ham Ninh Fishervillage, Highway 47</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D34" t="str">
-        <v/>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
       </c>
       <c r="E34">
         <v>10.1807795</v>
@@ -1087,18 +1515,18 @@
         <v>104.0489807</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="str">
-        <v>5 Tố</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Tỉnh Kiến Giang, Vietnam</v>
-      </c>
-      <c r="D35" t="str">
-        <v>ấp Suổc Mây</v>
+      <c r="B35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" t="s">
+        <v>53</v>
       </c>
       <c r="E35">
         <v>10.1799257</v>
@@ -1107,18 +1535,18 @@
         <v>103.9830979</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="str">
-        <v>126 Trần Hưng Đạo</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D36" t="str">
-        <v/>
+      <c r="B36" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
       </c>
       <c r="E36">
         <v>10.1916666</v>
@@ -1127,38 +1555,38 @@
         <v>103.9666622</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="str">
-        <v>91/10 Trần Hưng Đạo</v>
-      </c>
-      <c r="C37" t="str">
-        <v>Tỉnh Phu Quoc</v>
-      </c>
-      <c r="D37" t="str">
-        <v/>
+      <c r="B37" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
       </c>
       <c r="E37">
-        <v>10.2062289</v>
+        <v>10.206228899999999</v>
       </c>
       <c r="F37">
         <v>103.9660732</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="str">
-        <v>SK Hotel,MP-135 Marina Square, BIM Group, Ấp Đường Bào, Dương Tơ, Phú Quốc, Kiên Gia</v>
-      </c>
-      <c r="C38" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D38" t="str">
-        <v/>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
       </c>
       <c r="E38">
         <v>10.1098768</v>
@@ -1167,18 +1595,18 @@
         <v>103.9875052</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="str">
-        <v>98/1 Trần Hưng Đạo</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D39" t="str">
-        <v/>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
       </c>
       <c r="E39">
         <v>10.2013677</v>
@@ -1187,38 +1615,38 @@
         <v>103.9638987</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="str">
-        <v>180 Nguyễn Trung Trực</v>
-      </c>
-      <c r="C40" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D40" t="str">
-        <v/>
+      <c r="B40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
       </c>
       <c r="E40">
-        <v>10.2231572</v>
+        <v>10.223157199999999</v>
       </c>
       <c r="F40">
         <v>103.9669279</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="str">
-        <v>6 Lý Tự Trọng</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D41" t="str">
-        <v/>
+      <c r="B41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" t="s">
+        <v>11</v>
       </c>
       <c r="E41">
         <v>10.2165213</v>
@@ -1227,38 +1655,38 @@
         <v>103.960598</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="str">
-        <v>91/? Trần Hưng Đạo</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D42" t="str">
-        <v/>
+      <c r="B42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
       </c>
       <c r="E42">
-        <v>10.2059896</v>
+        <v>10.205989600000001</v>
       </c>
       <c r="F42">
         <v>103.9649213</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="str">
-        <v>149 Trần Hưng Đạo</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Tỉnh Kien Giang</v>
-      </c>
-      <c r="D43" t="str">
-        <v/>
+      <c r="B43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
       </c>
       <c r="E43">
         <v>10.192845</v>
@@ -1267,18 +1695,18 @@
         <v>103.9673382</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="str">
-        <v>63 Trần Hưng Đạo</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D44" t="str">
-        <v/>
+      <c r="B44" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
       </c>
       <c r="E44">
         <v>10.2106412</v>
@@ -1287,78 +1715,78 @@
         <v>103.9612848</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="str">
-        <v>81 Trần Hưng Đạo</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D45" t="str">
-        <v/>
+      <c r="B45" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
       </c>
       <c r="E45">
-        <v>10.2064309</v>
+        <v>10.206430900000001</v>
       </c>
       <c r="F45">
         <v>103.9632771</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="str">
-        <v>139 Trần Hưng Đạo</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D46" t="str">
-        <v/>
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
       </c>
       <c r="E46">
-        <v>10.1957867</v>
+        <v>10.195786699999999</v>
       </c>
       <c r="F46">
         <v>103.9681671</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="str">
-        <v>96 Nguyễn Trung Trực</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D47" t="str">
-        <v/>
+      <c r="B47" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
       </c>
       <c r="E47">
-        <v>10.2223052</v>
+        <v>10.222305199999999</v>
       </c>
       <c r="F47">
         <v>103.9625468</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="str">
-        <v>Alley 118 Alley 118, Tran Hung Dao Street</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D48" t="str">
-        <v/>
+      <c r="B48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
       </c>
       <c r="E48">
         <v>10.1949928</v>
@@ -1367,38 +1795,38 @@
         <v>103.9638958</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="str">
-        <v>141A Trần Hưng Đạo</v>
-      </c>
-      <c r="C49" t="str">
-        <v>Tỉnh Kien Giang</v>
-      </c>
-      <c r="D49" t="str">
-        <v>Khu Phố 7</v>
+      <c r="B49" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s">
+        <v>68</v>
       </c>
       <c r="E49">
-        <v>10.1952361</v>
+        <v>10.195236100000001</v>
       </c>
       <c r="F49">
-        <v>103.9682484</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>103.96824839999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="str">
-        <v>155 Trần Hưng Đạo</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Tỉnh Kien Giang</v>
-      </c>
-      <c r="D50" t="str">
-        <v>DƯƠNG ĐÔNG</v>
+      <c r="B50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" t="s">
+        <v>70</v>
       </c>
       <c r="E50">
         <v>10.1913418</v>
@@ -1407,138 +1835,138 @@
         <v>103.9670551</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="str">
-        <v>242 Nguyễn Trung Trực</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D51" t="str">
-        <v/>
+      <c r="B51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
       </c>
       <c r="E51">
-        <v>10.223308</v>
+        <v>10.223307999999999</v>
       </c>
       <c r="F51">
-        <v>103.972045</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>103.97204499999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="str">
-        <v>114 Trần Hưng Đạo</v>
-      </c>
-      <c r="C52" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D52" t="str">
-        <v/>
+      <c r="B52" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
       </c>
       <c r="E52">
-        <v>10.196074</v>
+        <v>10.196073999999999</v>
       </c>
       <c r="F52">
-        <v>103.9678343</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>103.96783430000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="str">
-        <v>69 Trần Hưng Đạo</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D53" t="str">
-        <v/>
+      <c r="B53" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" t="s">
+        <v>11</v>
       </c>
       <c r="E53">
-        <v>10.2082524</v>
+        <v>10.208252399999999</v>
       </c>
       <c r="F53">
         <v>103.9623165</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="str">
-        <v>157 Nguyễn Văn Cừ</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D54" t="str">
-        <v/>
+      <c r="B54" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>11</v>
       </c>
       <c r="E54">
-        <v>10.0218409</v>
+        <v>10.021840900000001</v>
       </c>
       <c r="F54">
         <v>104.0174325</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="str">
-        <v>136 Trần Hưng Đạo</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Tỉnh KIÊN GIANG</v>
-      </c>
-      <c r="D55" t="str">
-        <v>DƯƠNG TƠ</v>
+      <c r="B55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55" t="s">
+        <v>77</v>
       </c>
       <c r="E55">
-        <v>10.1875005</v>
+        <v>10.187500500000001</v>
       </c>
       <c r="F55">
-        <v>103.9689871</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>103.96898710000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="str">
-        <v>DĐ 37 Night Market</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D56" t="str">
-        <v/>
+      <c r="B56" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
       </c>
       <c r="E56">
-        <v>10.3255449</v>
+        <v>10.325544900000001</v>
       </c>
       <c r="F56">
-        <v>103.8576055</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>103.85760550000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="str">
-        <v>102 Trần Hưng Đạo</v>
-      </c>
-      <c r="C57" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D57" t="str">
-        <v/>
+      <c r="B57" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" t="s">
+        <v>11</v>
       </c>
       <c r="E57">
         <v>10.2004926</v>
@@ -1547,38 +1975,38 @@
         <v>103.9659121</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="str">
-        <v>111/9 Trần Hưng Đạo</v>
-      </c>
-      <c r="C58" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D58" t="str">
-        <v/>
+      <c r="B58" t="s">
+        <v>80</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
       </c>
       <c r="E58">
-        <v>10.2022381</v>
+        <v>10.202238100000001</v>
       </c>
       <c r="F58">
         <v>103.9667697</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="str">
-        <v>6 Mạc Cửu</v>
-      </c>
-      <c r="C59" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D59" t="str">
-        <v/>
+      <c r="B59" t="s">
+        <v>81</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>11</v>
       </c>
       <c r="E59">
         <v>10.2231407</v>
@@ -1587,18 +2015,18 @@
         <v>103.9625181</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="str">
-        <v>225 Trần Phú</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D60" t="str">
-        <v/>
+      <c r="B60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" t="s">
+        <v>11</v>
       </c>
       <c r="E60">
         <v>10.2318734</v>
@@ -1607,38 +2035,38 @@
         <v>103.9522746</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="str">
-        <v>5XQF+XHJ Kam pốt</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D61" t="str">
-        <v/>
+      <c r="B61" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>11</v>
       </c>
       <c r="E61">
-        <v>10.1900462</v>
+        <v>10.190046199999999</v>
       </c>
       <c r="F61">
         <v>103.9739117</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="str">
-        <v>32A Bạch Đằng</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D62" t="str">
-        <v/>
+      <c r="B62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C62" t="s">
+        <v>10</v>
+      </c>
+      <c r="D62" t="s">
+        <v>11</v>
       </c>
       <c r="E62">
         <v>10.2190332</v>
@@ -1647,118 +2075,118 @@
         <v>103.9584579</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="str">
-        <v>88/1 Trần Hưng Đạo</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D63" t="str">
-        <v/>
+      <c r="B63" t="s">
+        <v>85</v>
+      </c>
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" t="s">
+        <v>11</v>
       </c>
       <c r="E63">
-        <v>10.2044399</v>
+        <v>10.204439900000001</v>
       </c>
       <c r="F63">
         <v>103.9635936</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="str">
-        <v>99 Tran Hung Dao</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D64" t="str">
-        <v/>
+      <c r="B64" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" t="s">
+        <v>11</v>
       </c>
       <c r="E64">
-        <v>10.2042557</v>
+        <v>10.204255699999999</v>
       </c>
       <c r="F64">
-        <v>103.9644171</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>103.96441710000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="str">
-        <v>Số AT 96 Đại Lộ New An Thới</v>
-      </c>
-      <c r="C65" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D65" t="str">
-        <v>An Thới</v>
+      <c r="B65" t="s">
+        <v>87</v>
+      </c>
+      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" t="s">
+        <v>19</v>
       </c>
       <c r="E65">
-        <v>10.036319</v>
+        <v>10.036319000000001</v>
       </c>
       <c r="F65">
         <v>104.00693</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="str">
-        <v>118/3 Trần Hưng Đạo</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D66" t="str">
-        <v/>
+      <c r="B66" t="s">
+        <v>88</v>
+      </c>
+      <c r="C66" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
       </c>
       <c r="E66">
-        <v>10.1944376</v>
+        <v>10.194437600000001</v>
       </c>
       <c r="F66">
-        <v>103.9661896</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>103.96618960000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="str">
-        <v>Ấp 5 Đường Bào</v>
-      </c>
-      <c r="C67" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D67" t="str">
-        <v/>
+      <c r="B67" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
       </c>
       <c r="E67">
-        <v>10.1402332</v>
+        <v>10.140233200000001</v>
       </c>
       <c r="F67">
         <v>103.9940656</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="str">
-        <v>84 Trần Hưng Đạo</v>
-      </c>
-      <c r="C68" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D68" t="str">
-        <v/>
+      <c r="B68" t="s">
+        <v>90</v>
+      </c>
+      <c r="C68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
       </c>
       <c r="E68">
         <v>10.2050822</v>
@@ -1767,78 +2195,78 @@
         <v>103.9635213</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" t="str">
-        <v>ĐTH1-18 Địa Trung Hải 1</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Thành phố Phú Quốc</v>
-      </c>
-      <c r="D69" t="str">
-        <v>Grand World Phú Quốc</v>
+      <c r="B69" t="s">
+        <v>91</v>
+      </c>
+      <c r="C69" t="s">
+        <v>92</v>
+      </c>
+      <c r="D69" t="s">
+        <v>93</v>
       </c>
       <c r="E69">
-        <v>10.3246429</v>
+        <v>10.324642900000001</v>
       </c>
       <c r="F69">
         <v>103.8538358</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="str">
-        <v>54 Le Thuc Nha</v>
-      </c>
-      <c r="C70" t="str">
-        <v>Tỉnh Kien Giang</v>
-      </c>
-      <c r="D70" t="str">
-        <v>Ong Lang</v>
+      <c r="B70" t="s">
+        <v>94</v>
+      </c>
+      <c r="C70" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" t="s">
+        <v>95</v>
       </c>
       <c r="E70">
         <v>10.2656352</v>
       </c>
       <c r="F70">
-        <v>103.93483</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>103.93483000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="str">
-        <v>60-62 Nguyễn Văn Cừ</v>
-      </c>
-      <c r="C71" t="str">
-        <v>Tỉnh An Thoi</v>
-      </c>
-      <c r="D71" t="str">
-        <v/>
+      <c r="B71" t="s">
+        <v>96</v>
+      </c>
+      <c r="C71" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
       </c>
       <c r="E71">
         <v>10.0183546</v>
       </c>
       <c r="F71">
-        <v>104.0151512</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>104.01515120000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="str">
-        <v>100/3 Trần Hưng Đạo</v>
-      </c>
-      <c r="C72" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D72" t="str">
-        <v>Khu phố 7</v>
+      <c r="B72" t="s">
+        <v>98</v>
+      </c>
+      <c r="C72" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" t="s">
+        <v>99</v>
       </c>
       <c r="E72">
         <v>10.2001711</v>
@@ -1847,38 +2275,38 @@
         <v>103.9646577</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
-      <c r="B73" t="str">
-        <v>91/1 Trần Hưng Đạo</v>
-      </c>
-      <c r="C73" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D73" t="str">
-        <v/>
+      <c r="B73" t="s">
+        <v>100</v>
+      </c>
+      <c r="C73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
       </c>
       <c r="E73">
         <v>10.2065474</v>
       </c>
       <c r="F73">
-        <v>103.9658624</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>103.96586240000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
-      <c r="B74" t="str">
-        <v>2/1/118 Trần Hưng Đạo</v>
-      </c>
-      <c r="C74" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D74" t="str">
-        <v>Khu Phố 7</v>
+      <c r="B74" t="s">
+        <v>101</v>
+      </c>
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>68</v>
       </c>
       <c r="E74">
         <v>10.1948968</v>
@@ -1887,58 +2315,58 @@
         <v>103.9659163</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
-      <c r="B75" t="str">
-        <v>116 116 tran hung dao</v>
-      </c>
-      <c r="C75" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D75" t="str">
-        <v/>
+      <c r="B75" t="s">
+        <v>102</v>
+      </c>
+      <c r="C75" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
       </c>
       <c r="E75">
-        <v>10.1950893</v>
+        <v>10.195089299999999</v>
       </c>
       <c r="F75">
         <v>103.9673671</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="str">
-        <v>99 Tran Hung Dao</v>
-      </c>
-      <c r="C76" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D76" t="str">
-        <v/>
+      <c r="B76" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" t="s">
+        <v>11</v>
       </c>
       <c r="E76">
-        <v>10.2041175</v>
+        <v>10.204117500000001</v>
       </c>
       <c r="F76">
         <v>103.9644701</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="str">
-        <v>108 Đường 30/4</v>
-      </c>
-      <c r="C77" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D77" t="str">
-        <v/>
+      <c r="B77" t="s">
+        <v>103</v>
+      </c>
+      <c r="C77" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
       </c>
       <c r="E77">
         <v>10.2143388</v>
@@ -1947,58 +2375,58 @@
         <v>103.9668578</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
-      <c r="B78" t="str">
-        <v>77 khu phố 1 Nguyễn Trường Tộ</v>
-      </c>
-      <c r="C78" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D78" t="str">
-        <v/>
+      <c r="B78" t="s">
+        <v>104</v>
+      </c>
+      <c r="C78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
       </c>
       <c r="E78">
-        <v>10.0199802</v>
+        <v>10.019980199999999</v>
       </c>
       <c r="F78">
         <v>104.0114466</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" t="str">
-        <v>3 Bãi</v>
-      </c>
-      <c r="C79" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D79" t="str">
-        <v>Ông Lang</v>
+      <c r="B79" t="s">
+        <v>105</v>
+      </c>
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>106</v>
       </c>
       <c r="E79">
         <v>10.266</v>
       </c>
       <c r="F79">
-        <v>103.9291</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>103.92910000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" t="str">
-        <v>Tổ 7, Ấp Suối Đá Tuyến tránh Dương Đông</v>
-      </c>
-      <c r="C80" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D80" t="str">
-        <v>Xã Dương Tơ</v>
+      <c r="B80" t="s">
+        <v>107</v>
+      </c>
+      <c r="C80" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" t="s">
+        <v>108</v>
       </c>
       <c r="E80">
         <v>10.2114403</v>
@@ -2007,18 +2435,18 @@
         <v>103.9951427</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
-      <c r="B81" t="str">
-        <v>100 Trần Hưng Đạo</v>
-      </c>
-      <c r="C81" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D81" t="str">
-        <v/>
+      <c r="B81" t="s">
+        <v>109</v>
+      </c>
+      <c r="C81" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
       </c>
       <c r="E81">
         <v>10.2000362</v>
@@ -2027,38 +2455,38 @@
         <v>103.9672589</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
-      <c r="B82" t="str">
-        <v>106 Tran Hung Dao</v>
-      </c>
-      <c r="C82" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D82" t="str">
-        <v/>
+      <c r="B82" t="s">
+        <v>110</v>
+      </c>
+      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
       </c>
       <c r="E82">
-        <v>10.1988303</v>
+        <v>10.198830299999999</v>
       </c>
       <c r="F82">
         <v>103.9679574</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
-      <c r="B83" t="str">
-        <v>62 Trần Hưng Đạo</v>
-      </c>
-      <c r="C83" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D83" t="str">
-        <v/>
+      <c r="B83" t="s">
+        <v>111</v>
+      </c>
+      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" t="s">
+        <v>11</v>
       </c>
       <c r="E83">
         <v>10.2084134</v>
@@ -2067,58 +2495,58 @@
         <v>103.961314</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
-      <c r="B84" t="str">
-        <v>19 Venice Street</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D84" t="str">
-        <v>Sunset Town</v>
+      <c r="B84" t="s">
+        <v>112</v>
+      </c>
+      <c r="C84" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" t="s">
+        <v>8</v>
       </c>
       <c r="E84">
-        <v>10.0308471</v>
+        <v>10.030847100000001</v>
       </c>
       <c r="F84">
         <v>104.0054519</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
-      <c r="B85" t="str">
-        <v>127/2 Trần Hưng Đạo</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D85" t="str">
-        <v>Dương Đông</v>
+      <c r="B85" t="s">
+        <v>113</v>
+      </c>
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" t="s">
+        <v>29</v>
       </c>
       <c r="E85">
         <v>10.1989991</v>
       </c>
       <c r="F85">
-        <v>103.9685924</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>103.96859240000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
-      <c r="B86" t="str">
-        <v>47/9 Trần Hưng Đạo</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D86" t="str">
-        <v>Dương Đông</v>
+      <c r="B86" t="s">
+        <v>114</v>
+      </c>
+      <c r="C86" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" t="s">
+        <v>29</v>
       </c>
       <c r="E86">
         <v>10.2130163</v>
@@ -2127,138 +2555,138 @@
         <v>103.9598032</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
-      <c r="B87" t="str">
-        <v>1 Trần Hưng Đạo</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D87" t="str">
-        <v/>
+      <c r="B87" t="s">
+        <v>115</v>
+      </c>
+      <c r="C87" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87" t="s">
+        <v>11</v>
       </c>
       <c r="E87">
-        <v>10.1833023</v>
+        <v>10.183302299999999</v>
       </c>
       <c r="F87">
         <v>103.9689147</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
-      <c r="B88" t="str">
-        <v>tổ 7 đường Dinh Bà</v>
-      </c>
-      <c r="C88" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D88" t="str">
-        <v/>
+      <c r="B88" t="s">
+        <v>116</v>
+      </c>
+      <c r="C88" t="s">
+        <v>10</v>
+      </c>
+      <c r="D88" t="s">
+        <v>11</v>
       </c>
       <c r="E88">
-        <v>10.2565582</v>
+        <v>10.256558200000001</v>
       </c>
       <c r="F88">
-        <v>103.9440485</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>103.94404849999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
-      <c r="B89" t="str">
-        <v>105 Trần Hưng Đạo</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D89" t="str">
-        <v/>
+      <c r="B89" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" t="s">
+        <v>11</v>
       </c>
       <c r="E89">
         <v>10.2030844</v>
       </c>
       <c r="F89">
-        <v>103.96457</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>103.96456999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
-      <c r="B90" t="str">
-        <v>81 b Trần Hưng Đạo</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D90" t="str">
-        <v/>
+      <c r="B90" t="s">
+        <v>117</v>
+      </c>
+      <c r="C90" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" t="s">
+        <v>11</v>
       </c>
       <c r="E90">
-        <v>10.2081776</v>
+        <v>10.208177600000001</v>
       </c>
       <c r="F90">
         <v>103.9623759</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
-      <c r="B91" t="str">
-        <v>99A Tran Hung Dao</v>
-      </c>
-      <c r="C91" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D91" t="str">
-        <v/>
+      <c r="B91" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" t="s">
+        <v>11</v>
       </c>
       <c r="E91">
-        <v>10.2039719</v>
+        <v>10.203971900000001</v>
       </c>
       <c r="F91">
         <v>103.9644966</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
-      <c r="B92" t="str">
-        <v>149 Trần Hưng Đạo</v>
-      </c>
-      <c r="C92" t="str">
-        <v>Tỉnh Kien Giang</v>
-      </c>
-      <c r="D92" t="str">
-        <v/>
+      <c r="B92" t="s">
+        <v>46</v>
+      </c>
+      <c r="C92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" t="s">
+        <v>11</v>
       </c>
       <c r="E92">
-        <v>10.1929805</v>
+        <v>10.192980500000001</v>
       </c>
       <c r="F92">
         <v>103.9674062</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
-      <c r="B93" t="str">
-        <v>01 Cầu Bà Phong Trần Hưng Đạo</v>
-      </c>
-      <c r="C93" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D93" t="str">
-        <v/>
+      <c r="B93" t="s">
+        <v>35</v>
+      </c>
+      <c r="C93" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" t="s">
+        <v>11</v>
       </c>
       <c r="E93">
         <v>10.1849419</v>
@@ -2267,38 +2695,38 @@
         <v>103.968203</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
-      <c r="B94" t="str">
-        <v>118/2 Trần Hưng Đạo</v>
-      </c>
-      <c r="C94" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D94" t="str">
-        <v/>
+      <c r="B94" t="s">
+        <v>119</v>
+      </c>
+      <c r="C94" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" t="s">
+        <v>11</v>
       </c>
       <c r="E94">
-        <v>10.1944323</v>
+        <v>10.194432300000001</v>
       </c>
       <c r="F94">
-        <v>103.967024</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>103.96702399999999</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
-      <c r="B95" t="str">
-        <v>SS13-S01 Khu phố đi bộ Sona sea, Phú Quốc</v>
-      </c>
-      <c r="C95" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D95" t="str">
-        <v/>
+      <c r="B95" t="s">
+        <v>120</v>
+      </c>
+      <c r="C95" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" t="s">
+        <v>11</v>
       </c>
       <c r="E95">
         <v>10.1303717</v>
@@ -2307,58 +2735,58 @@
         <v>103.9833819</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
-      <c r="B96" t="str">
-        <v>H1-H2 Cầu Hôn</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D96" t="str">
-        <v/>
+      <c r="B96" t="s">
+        <v>121</v>
+      </c>
+      <c r="C96" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" t="s">
+        <v>11</v>
       </c>
       <c r="E96">
         <v>10.0294436</v>
       </c>
       <c r="F96">
-        <v>104.00893</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>104.00893000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
-      <c r="B97" t="str">
-        <v>127D Trần Hưng Đạo</v>
-      </c>
-      <c r="C97" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D97" t="str">
-        <v/>
+      <c r="B97" t="s">
+        <v>48</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" t="s">
+        <v>11</v>
       </c>
       <c r="E97">
-        <v>10.198946</v>
+        <v>10.198945999999999</v>
       </c>
       <c r="F97">
-        <v>103.9685821</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>103.96858210000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
-      <c r="B98" t="str">
-        <v>5 Trần Hưng Đạo</v>
-      </c>
-      <c r="C98" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D98" t="str">
-        <v/>
+      <c r="B98" t="s">
+        <v>122</v>
+      </c>
+      <c r="C98" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" t="s">
+        <v>11</v>
       </c>
       <c r="E98">
         <v>10.2073193</v>
@@ -2367,18 +2795,18 @@
         <v>103.9627871</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
-      <c r="B99" t="str">
-        <v>143 Tran Hung Dao Street</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Tỉnh Phu Quoc Island</v>
-      </c>
-      <c r="D99" t="str">
-        <v/>
+      <c r="B99" t="s">
+        <v>123</v>
+      </c>
+      <c r="C99" t="s">
+        <v>45</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
       </c>
       <c r="E99">
         <v>10.1943746</v>
@@ -2387,18 +2815,18 @@
         <v>103.967753</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
-      <c r="B100" t="str">
-        <v>43 Trần Hưng Đạo</v>
-      </c>
-      <c r="C100" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D100" t="str">
-        <v/>
+      <c r="B100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C100" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" t="s">
+        <v>11</v>
       </c>
       <c r="E100">
         <v>10.2132357</v>
@@ -2407,58 +2835,58 @@
         <v>103.9592663</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
-      <c r="B101" t="str">
-        <v>143 Trần Hưng Đạo</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Tỉnh Kien Giang</v>
-      </c>
-      <c r="D101" t="str">
-        <v/>
+      <c r="B101" t="s">
+        <v>43</v>
+      </c>
+      <c r="C101" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" t="s">
+        <v>11</v>
       </c>
       <c r="E101">
-        <v>10.1939605</v>
+        <v>10.193960499999999</v>
       </c>
       <c r="F101">
         <v>103.9671139</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
-      <c r="B102" t="str">
-        <v>91/4 Trần Hưng Đạo</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D102" t="str">
-        <v/>
+      <c r="B102" t="s">
+        <v>125</v>
+      </c>
+      <c r="C102" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" t="s">
+        <v>11</v>
       </c>
       <c r="E102">
-        <v>10.2054208</v>
+        <v>10.205420800000001</v>
       </c>
       <c r="F102">
         <v>103.9647538</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
-      <c r="B103" t="str">
-        <v>136 Trần Hưng Đạo</v>
-      </c>
-      <c r="C103" t="str">
-        <v>Tỉnh KIÊN GIANG</v>
-      </c>
-      <c r="D103" t="str">
-        <v>DƯƠNG TƠ</v>
+      <c r="B103" t="s">
+        <v>75</v>
+      </c>
+      <c r="C103" t="s">
+        <v>76</v>
+      </c>
+      <c r="D103" t="s">
+        <v>77</v>
       </c>
       <c r="E103">
         <v>10.1881994</v>
@@ -2467,18 +2895,18 @@
         <v>103.9693429</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
-      <c r="B104" t="str">
-        <v>118/18 Trần Hưng Đạo</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D104" t="str">
-        <v/>
+      <c r="B104" t="s">
+        <v>126</v>
+      </c>
+      <c r="C104" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" t="s">
+        <v>11</v>
       </c>
       <c r="E104">
         <v>10.1929765</v>
@@ -2487,58 +2915,58 @@
         <v>103.9645215</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
-      <c r="B105" t="str">
-        <v>100 Trần Hưng Đạo</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D105" t="str">
-        <v/>
+      <c r="B105" t="s">
+        <v>109</v>
+      </c>
+      <c r="C105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
       </c>
       <c r="E105">
-        <v>10.2016865</v>
+        <v>10.201686499999999</v>
       </c>
       <c r="F105">
         <v>103.9644464</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
-      <c r="B106" t="str">
-        <v>141 Trần Hưng Đạo</v>
-      </c>
-      <c r="C106" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D106" t="str">
-        <v/>
+      <c r="B106" t="s">
+        <v>127</v>
+      </c>
+      <c r="C106" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" t="s">
+        <v>11</v>
       </c>
       <c r="E106">
         <v>10.1956954</v>
       </c>
       <c r="F106">
-        <v>103.9681725</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>103.96817249999999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
-      <c r="B107" t="str">
-        <v>1 Đường Trần Hưng Đạo</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D107" t="str">
-        <v>Khu Phố Dương Tơ</v>
+      <c r="B107" t="s">
+        <v>128</v>
+      </c>
+      <c r="C107" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" t="s">
+        <v>129</v>
       </c>
       <c r="E107">
         <v>10.1672628</v>
@@ -2547,38 +2975,38 @@
         <v>103.9752372</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
-      <c r="B108" t="str">
-        <v>Tổ 3 Lê Thúc Nha</v>
-      </c>
-      <c r="C108" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D108" t="str">
-        <v>ấp Ông Lang</v>
+      <c r="B108" t="s">
+        <v>130</v>
+      </c>
+      <c r="C108" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" t="s">
+        <v>131</v>
       </c>
       <c r="E108">
-        <v>10.262797</v>
+        <v>10.262797000000001</v>
       </c>
       <c r="F108">
         <v>103.9392304</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
-      <c r="B109" t="str">
-        <v>3 Đường tỉnh 975</v>
-      </c>
-      <c r="C109" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D109" t="str">
-        <v/>
+      <c r="B109" t="s">
+        <v>132</v>
+      </c>
+      <c r="C109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" t="s">
+        <v>11</v>
       </c>
       <c r="E109">
         <v>10.1157158</v>
@@ -2587,18 +3015,18 @@
         <v>103.9842833</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
-      <c r="B110" t="str">
-        <v>6 Bạch Đằng</v>
-      </c>
-      <c r="C110" t="str">
-        <v>Tỉnh Dương Đông</v>
-      </c>
-      <c r="D110" t="str">
-        <v/>
+      <c r="B110" t="s">
+        <v>133</v>
+      </c>
+      <c r="C110" t="s">
+        <v>134</v>
+      </c>
+      <c r="D110" t="s">
+        <v>11</v>
       </c>
       <c r="E110">
         <v>10.2177647</v>
@@ -2607,18 +3035,18 @@
         <v>103.9585934</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
-      <c r="B111" t="str">
-        <v>121 Trần Hưng Đạo</v>
-      </c>
-      <c r="C111" t="str">
-        <v>Tỉnh Dương Đông</v>
-      </c>
-      <c r="D111" t="str">
-        <v>Kiên Giang</v>
+      <c r="B111" t="s">
+        <v>135</v>
+      </c>
+      <c r="C111" t="s">
+        <v>134</v>
+      </c>
+      <c r="D111" t="s">
+        <v>136</v>
       </c>
       <c r="E111">
         <v>10.2005006</v>
@@ -2627,129 +3055,130 @@
         <v>103.9679275</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
-      <c r="B112" t="str">
-        <v>100C/4 Trần Hưng Đạo</v>
-      </c>
-      <c r="C112" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D112" t="str">
-        <v>Dương Đông</v>
+      <c r="B112" t="s">
+        <v>28</v>
+      </c>
+      <c r="C112" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" t="s">
+        <v>29</v>
       </c>
       <c r="E112">
-        <v>10.2001894</v>
+        <v>10.200189399999999</v>
       </c>
       <c r="F112">
-        <v>103.9645329</v>
-      </c>
-    </row>
-    <row r="113">
+        <v>103.96453289999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" t="str">
-        <v>126 Trần Hưng Đạo</v>
-      </c>
-      <c r="C113" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D113" t="str">
-        <v/>
+      <c r="B113" t="s">
+        <v>54</v>
+      </c>
+      <c r="C113" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113" t="s">
+        <v>11</v>
       </c>
       <c r="E113">
-        <v>10.1998486</v>
+        <v>10.199848599999999</v>
       </c>
       <c r="F113">
         <v>103.9675148</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
-      <c r="B114" t="str">
-        <v>Lot 4 Ong Lang Hamlet</v>
-      </c>
-      <c r="C114" t="str">
-        <v>Tỉnh An Giang</v>
-      </c>
-      <c r="D114" t="str">
-        <v/>
+      <c r="B114" t="s">
+        <v>137</v>
+      </c>
+      <c r="C114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114" t="s">
+        <v>11</v>
       </c>
       <c r="E114">
-        <v>10.2626973</v>
+        <v>10.262697299999999</v>
       </c>
       <c r="F114">
-        <v>103.9402342</v>
-      </c>
-    </row>
-    <row r="115">
+        <v>103.94023420000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
-      <c r="B115" t="str">
-        <v>100C/4A Trần Hưng Đạo</v>
-      </c>
-      <c r="C115" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D115" t="str">
-        <v>Dương Đông</v>
+      <c r="B115" t="s">
+        <v>138</v>
+      </c>
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" t="s">
+        <v>29</v>
       </c>
       <c r="E115">
-        <v>10.2002838</v>
+        <v>10.200283799999999</v>
       </c>
       <c r="F115">
-        <v>103.9645557</v>
-      </c>
-    </row>
-    <row r="116">
+        <v>103.96455570000001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
-      <c r="B116" t="str">
-        <v>Hamlet 4 Cua Can Commune</v>
-      </c>
-      <c r="C116" t="str">
-        <v>Tỉnh Vietnam</v>
-      </c>
-      <c r="D116" t="str">
-        <v/>
+      <c r="B116" t="s">
+        <v>139</v>
+      </c>
+      <c r="C116" t="s">
+        <v>140</v>
+      </c>
+      <c r="D116" t="s">
+        <v>11</v>
       </c>
       <c r="E116">
         <v>10.3039378</v>
       </c>
       <c r="F116">
-        <v>103.8609159</v>
-      </c>
-    </row>
-    <row r="117">
+        <v>103.86091589999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
-      <c r="B117" t="str">
-        <v>233 Nguyễn Trung Trực</v>
-      </c>
-      <c r="C117" t="str">
-        <v>Tỉnh Kiên Giang</v>
-      </c>
-      <c r="D117" t="str">
-        <v>khu phố 5</v>
+      <c r="B117" t="s">
+        <v>141</v>
+      </c>
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" t="s">
+        <v>142</v>
       </c>
       <c r="E117">
-        <v>10.2235033</v>
+        <v>10.223503300000001</v>
       </c>
       <c r="F117">
-        <v>103.968747</v>
+        <v>103.96874699999999</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F117"/>
+    <ignoredError sqref="A1:F117" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>